--- a/plans/AI产品经理工具栈与信息源.xlsx
+++ b/plans/AI产品经理工具栈与信息源.xlsx
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'必装软件'!$A$1:$G$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GitHub学习项目'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GitHub学习项目'!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'关注网站'!$A$1:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'上手顺序'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'全栈开发'!$A$1:$G$14</definedName>
@@ -2961,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3103,27 +3103,27 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>提示词与上下文工程</t>
+          <t>★ Agent 开发母本</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>dair-ai/Prompt-Engineering-Guide</t>
+          <t>datawhalechina/hello-agents（《从零开始构建智能体》）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78.5k</t>
+          <t>81.0k</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>提示词、上下文工程、RAG、AI Agent 的系统指南</t>
+          <t>16 章中文教程 + 每章可运行代码 + 14 篇补充（面试题/上下文工程/评估/Skill）+ 55 个社区共创 Agent 项目</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>第 1 周起当手册，随用随查</t>
+          <t>★ 已入库本地 D:\code\hello-agents（索引见 docs/hello-agents-学习索引.md）：做 L2 精读第八章，做 L3 精读第四/七/九/十四章并跑 code/chapter14 参考实现</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3135,59 +3135,59 @@
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中文 LLM 入门</t>
+          <t>提示词与上下文工程</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>datawhalechina/llm-cookbook</t>
+          <t>dair-ai/Prompt-Engineering-Guide</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24.7k</t>
+          <t>78.5k</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>吴恩达大模型系列课程中文版</t>
+          <t>提示词、上下文工程、RAG、AI Agent 的系统指南</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>英文吃力时优先看这个</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>推荐</t>
+          <t>第 1 周起当手册，随用随查</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>必学</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Agent 官方课程</t>
+          <t>中文 LLM 入门</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>huggingface/agents-course</t>
+          <t>datawhalechina/llm-cookbook</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32.7k</t>
+          <t>24.7k</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face 官方 Agent 课程</t>
+          <t>吴恩达大模型系列课程中文版</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>系统学 Agent 时用</t>
+          <t>英文吃力时优先看这个</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3199,27 +3199,27 @@
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中文 LLM 资源</t>
+          <t>Agent 官方课程</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>WangRongsheng/awesome-LLM-resources</t>
+          <t>huggingface/agents-course</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9.0k</t>
+          <t>32.7k</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>多模态、Agent、辅助编程、MCP 等中文资料汇总</t>
+          <t>Hugging Face 官方 Agent 课程</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>找中文资料的第一站</t>
+          <t>系统学 Agent 时用</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3231,27 +3231,27 @@
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中文模型/生态</t>
+          <t>中文 LLM 资源</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AiHubCN/Awesome-Chinese-LLM</t>
+          <t>WangRongsheng/awesome-LLM-resources</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22.8k</t>
+          <t>9.0k</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>中文大模型、垂直微调、数据集与教程</t>
+          <t>多模态、Agent、辅助编程、MCP 等中文资料汇总</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>做中文场景时查</t>
+          <t>找中文资料的第一站</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3263,27 +3263,27 @@
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Agent 项目清单</t>
+          <t>中文模型/生态</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>e2b-dev/awesome-ai-agents</t>
+          <t>AiHubCN/Awesome-Chinese-LLM</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>30.1k</t>
+          <t>22.8k</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>自主 Agent 项目大全</t>
+          <t>中文大模型、垂直微调、数据集与教程</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>找 L3/L4 项目灵感</t>
+          <t>做中文场景时查</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3295,27 +3295,27 @@
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>工程化落地</t>
+          <t>Agent 项目清单</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>liguodongiot/llm-action</t>
+          <t>e2b-dev/awesome-ai-agents</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25.1k</t>
+          <t>30.1k</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>大模型工程化与应用落地的实战经验</t>
+          <t>自主 Agent 项目大全</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>做 L4 平台项目时看</t>
+          <t>找 L3/L4 项目灵感</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3327,32 +3327,32 @@
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>★ 学产品设计</t>
+          <t>工程化落地</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>asgeirtj/system_prompts_leaks</t>
+          <t>liguodongiot/llm-action</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68.0k</t>
+          <t>25.1k</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>各大 AI 产品的真实系统提示词</t>
+          <t>大模型工程化与应用落地的实战经验</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>★ 看顶级 AI 产品怎么设计提示词与边界——这是 AI PM 独有的学习材料</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>必学</t>
+          <t>做 L4 平台项目时看</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>推荐</t>
         </is>
       </c>
     </row>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>x1xhlol/system-prompts-and-models-of-ai-tools</t>
+          <t>asgeirtj/system_prompts_leaks</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>143.8k</t>
+          <t>68.0k</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cursor/Claude Code/Devin/Manus 等工具的系统提示词与内部工具</t>
+          <t>各大 AI 产品的真实系统提示词</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>同上，更全；做产品时对照它怎么约束模型行为</t>
+          <t>★ 看顶级 AI 产品怎么设计提示词与边界——这是 AI PM 独有的学习材料</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -3391,27 +3391,27 @@
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中文 PM 知识库</t>
+          <t>★ 学产品设计</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>archlizheng/AIPM-Wiki</t>
+          <t>x1xhlol/system-prompts-and-models-of-ai-tools</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>143.8k</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>AI 产品经理入门：面试题库 · AI 基础 · 案例拆解 · 学习路线</t>
+          <t>Cursor/Claude Code/Devin/Manus 等工具的系统提示词与内部工具</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>★ 与你的目标完全对口，中文，先通读一遍</t>
+          <t>同上，更全；做产品时对照它怎么约束模型行为</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -3423,76 +3423,108 @@
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>读代码库</t>
+          <t>中文 PM 知识库</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The-Pocket/PocketFlow-Tutorial-Codebase-Knowledge</t>
+          <t>archlizheng/AIPM-Wiki</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12.7k</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>把代码库变成教程的方法</t>
+          <t>AI 产品经理入门：面试题库 · AI 基础 · 案例拆解 · 学习路线</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>读开源项目源码时用它当方法</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>可选</t>
+          <t>★ 与你的目标完全对口，中文，先通读一遍</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>必学</t>
         </is>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>读代码库</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>The-Pocket/PocketFlow-Tutorial-Codebase-Knowledge</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12.7k</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>把代码库变成教程的方法</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>读开源项目源码时用它当方法</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>评测与可观测</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>langfuse/langfuse</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>34.9k</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>怎么给 LLM 应用做追踪与评测</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>做 L1 评测时边用边学</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>★ 最该先看两个：awesome-llm-apps（找参考实现）+ AIPM-Wiki（中文入门）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4576,12 +4608,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>LangGraph · browser-use · Firecrawl · CrewAI</t>
+          <t>LangGraph · browser-use · Firecrawl · CrewAI · 本地母本 hello-agents（第四/七/九/十四章）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>L3 是 Agent 编排，这四样是地基</t>
+          <t>L3 是 Agent 编排，这四样是地基；母本提供可运行参考实现，不用从零摸</t>
         </is>
       </c>
     </row>
